--- a/public/crawlability-zen-house-september-2026.xlsx
+++ b/public/crawlability-zen-house-september-2026.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של zen-house ב-SE Ranking (הסריקה האחרונה: 2026-06-08).</t>
+          <t>להריץ מחדש את ה-Website Audit של zen-house ב-SE Ranking (הסריקה האחרונה: 2026-06-08); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-zen-house-september-2026.xlsx
+++ b/public/crawlability-zen-house-september-2026.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/public/crawlability-zen-house-september-2026.xlsx
+++ b/public/crawlability-zen-house-september-2026.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">

--- a/public/crawlability-zen-house-september-2026.xlsx
+++ b/public/crawlability-zen-house-september-2026.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות (הבולטת: https://zen-house.co.il/treatments/עיסוי-תאילנדי/, 28 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות; הבולטת https://zen-house.co.il/treatments/עיסוי-תאילנדי/ (28 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של zen-house ב-SE Ranking (הסריקה האחרונה: 2026-06-08); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של zen-house ב-SE Ranking; הסריקה האחרונה: 2026-06-08.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-zen-house-september-2026.xlsx
+++ b/public/crawlability-zen-house-september-2026.xlsx
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,11 +62,6 @@
         <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -80,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -91,14 +86,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,36 +494,6 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות; הבולטת https://zen-house.co.il/treatments/עיסוי-תאילנדי/ (28 קישורים נכנסים).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של zen-house ב-SE Ranking; הסריקה האחרונה: 2026-06-08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>להחליט אם להסיר את חסימת סורקי ה-AI (GPTBot, Google-Extended, Applebot-Extended, CCBot, Amazonbot, meta-externalagent, Bytespider) בקובץ robots.txt.</t>
         </is>
       </c>
     </row>
@@ -620,7 +582,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/treatments/עיסוי-תאילנדי/</t>
         </is>
@@ -633,7 +595,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/treatments/עיסוי-תאילנדי-עם-שמן/</t>
         </is>
@@ -644,7 +606,7 @@
       <c r="F2" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/
 https://zen-house.co.il/אודות/
@@ -669,7 +631,7 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/treatments/עיסוי-תאילנדי-עם-שמן/</t>
         </is>
@@ -681,7 +643,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/בית/</t>
         </is>
@@ -694,7 +656,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/</t>
         </is>
@@ -705,7 +667,7 @@
       <c r="F3" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/
 https://zen-house.co.il/אודות/
@@ -730,7 +692,7 @@
           <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/</t>
         </is>
@@ -742,7 +704,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il//מדיניות-פרטיות/</t>
         </is>
@@ -755,7 +717,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/מדיניות-פרטיות/</t>
         </is>
@@ -766,7 +728,7 @@
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/</t>
         </is>
@@ -781,12 +743,12 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/מדיניות-פרטיות/</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -877,7 +839,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/cdn-cgi/l/email-protection</t>
         </is>
@@ -897,7 +859,7 @@
       <c r="F2" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/
 https://zen-house.co.il/הצהרת-נגישות/
@@ -923,7 +885,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -1000,7 +962,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/sitemap_index.xml</t>
         </is>
@@ -1054,7 +1016,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/sitemap_index.xml</t>
         </is>
@@ -1076,7 +1038,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/post-sitemap.xml</t>
         </is>
@@ -1098,7 +1060,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/page-sitemap.xml</t>
         </is>
@@ -1120,7 +1082,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/treatments-sitemap.xml</t>
         </is>
@@ -1142,7 +1104,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/category-sitemap.xml</t>
         </is>
@@ -1164,7 +1126,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/sitemap.xml</t>
         </is>
@@ -1186,7 +1148,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/wp-sitemap.xml</t>
         </is>
@@ -1225,7 +1187,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/</t>
         </is>
@@ -1235,7 +1197,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/ (0 הפניות)</t>
         </is>
@@ -1247,7 +1209,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>http://zen-house.co.il/</t>
         </is>
@@ -1257,7 +1219,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/ (1 הפניות)</t>
         </is>
@@ -1269,7 +1231,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>https://www.zen-house.co.il/</t>
         </is>
@@ -1279,7 +1241,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/ (1 הפניות)</t>
         </is>
@@ -1291,7 +1253,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>http://www.zen-house.co.il/</t>
         </is>
@@ -1301,7 +1263,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/ (2 הפניות)</t>
         </is>
@@ -1354,7 +1316,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>https://zen-house.co.il/</t>
         </is>
